--- a/data/merged/2026-09-28/MERGED_US_Robot-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_US_Robot-Vacuum_2026-09-28.xlsx
@@ -8005,94 +8005,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8418,7 +8330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -20067,303 +19979,35 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0H2V9LVLF</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Size: 8 Fl Oz (Pack of 2)</t>
+          <t>Color: Coral Black</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Brand: eufy | Item Form: Liquid | Scent: Unscented | Specific Uses For Product: Floor | Material Feature: Non-Toxic</t>
+          <t>Brand: wrydao | Model Name: H6 Pro | Surface Recommendation: Carpet Hard Floor Wood Tile | Special Feature: Advanced Custom Cleaning, Anti-Collision, Anti-Fall, Auto-Docking, Automatic Dust Collection, Pet Hair Pick Up | Color: Coral Black</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>eufy</t>
+          <t>wrydao</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0H2V9LVLF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>eufy RoboVac Hard Floor Cleaning Solution (2 Bottles), Dilution Ratio 1:200, 473 ml, Floor Cleaner, Plant-Based,Compatible with Omni C20, X8 Pro, X10 Omni, G series, L Series</t>
+          <t>Robot Vacuum and Mop Self Emptying: 6000Pa Robotic Vacuum with Mapping, 90 Days Hands-Free Cleaning, LIDAR Navigation, Alexa/APP Control, 3-in-1 Robot Vacuum for Pet Hair Hard Floor Carpet Home</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
-        <is>
-          <t>Tough on Stains - Effortlessly lift dirt, grime, grease, and tough stains off hard surfaces to make cleanup easier.
-Ideal for All Hard Floors - Versatile and safe to use on different finishings around the house, including tile, ceramic, marble, laminate, vinyl, and more.
-Friendly Formula - The cleaning solution specially developed formula made from plants.
-Clean Finish - Turn streaky-clean messes to squeaky-clean floors with this reduced foaming formula that leaves a clean, consistent finish every time.
-Perfect Match - Eufy Accessories compatible with X10 Pro Omni, Omni C20, X8 Pro, X9 Pro, X8 Hybrid, L60 Hybrid, L70, L35 Hybrid, G30 Hybrid Series, G40 Hybrid Series. More deep cleaning and less deep worrying for you.</t>
-        </is>
-      </c>
-      <c r="J44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0C7C7PLLG?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="14" t="inlineStr">
-        <is>
-          <t>B0GHNFPSLP</t>
-        </is>
-      </c>
-      <c r="M44" s="14" t="inlineStr">
-        <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N44" s="14" t="inlineStr">
-        <is>
-          <t>Industrial &amp; Scientific</t>
-        </is>
-      </c>
-      <c r="O44" s="15">
-        <v>2493</v>
-      </c>
-      <c r="P44" s="15">
-        <v>-353</v>
-      </c>
-      <c r="Q44" s="16">
-        <v>-0.2</v>
-      </c>
-      <c r="R44" s="17" t="inlineStr">
-        <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S44" s="18" t="inlineStr">
-        <is>
-          <t>5
-18</t>
-        </is>
-      </c>
-      <c r="T44" s="15">
-        <v>2571</v>
-      </c>
-      <c r="U44" s="16">
-        <v>-0.23</v>
-      </c>
-      <c r="V44" s="15">
-        <v>77104</v>
-      </c>
-      <c r="W44" s="15" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="X44" s="15">
-        <v>53660</v>
-      </c>
-      <c r="Y44" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z44" s="20">
-        <v>29.99</v>
-      </c>
-      <c r="AA44" s="4"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="15"/>
-      <c r="AD44" s="19">
-        <v>1515</v>
-      </c>
-      <c r="AE44" s="15">
-        <v>30</v>
-      </c>
-      <c r="AF44" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG44" s="22">
-        <v>0.011699999999999999</v>
-      </c>
-      <c r="AH44" s="20">
-        <v>6.31</v>
-      </c>
-      <c r="AI44" s="16">
-        <v>0.67</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="13" t="inlineStr">
-        <is>
-          <t>2023-06-30</t>
-        </is>
-      </c>
-      <c r="AL44" s="19">
-        <v>1186</v>
-      </c>
-      <c r="AM44" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN44" s="13" t="inlineStr">
-        <is>
-          <t>6天</t>
-        </is>
-      </c>
-      <c r="AO44" s="13" t="inlineStr">
-        <is>
-          <t>2天</t>
-        </is>
-      </c>
-      <c r="AP44" s="4"/>
-      <c r="AQ44" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR44" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS44" s="14" t="inlineStr">
-        <is>
-          <t>Anker EufyHome</t>
-        </is>
-      </c>
-      <c r="AT44" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>WA 98004 US</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3</t>
-        </is>
-      </c>
-      <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ44" s="13"/>
-      <c r="BA44" s="13"/>
-      <c r="BB44" s="13"/>
-      <c r="BC44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE44" s="13"/>
-      <c r="BF44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG44" s="13"/>
-      <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ44" s="23" t="inlineStr">
-        <is>
-          <t>2.3 pounds</t>
-        </is>
-      </c>
-      <c r="BK44" s="23" t="inlineStr">
-        <is>
-          <t>1.04 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="23" t="inlineStr">
-        <is>
-          <t>8.8 x 4.4 x 2 inches</t>
-        </is>
-      </c>
-      <c r="BM44" s="23" t="inlineStr">
-        <is>
-          <t>22.35 x 11.18 x 5.08 cm</t>
-        </is>
-      </c>
-      <c r="BN44" s="23" t="inlineStr">
-        <is>
-          <t>2.38 pounds</t>
-        </is>
-      </c>
-      <c r="BO44" s="23" t="inlineStr">
-        <is>
-          <t>1.08 kg</t>
-        </is>
-      </c>
-      <c r="BP44" s="23" t="inlineStr">
-        <is>
-          <t>8.9 x 4.5 x 4 inches</t>
-        </is>
-      </c>
-      <c r="BQ44" s="23" t="inlineStr">
-        <is>
-          <t>22.61 x 11.43 x 10.16 cm</t>
-        </is>
-      </c>
-      <c r="BR44" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13">
-        <v>44</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>B0H2V9LVLF</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Color: Coral Black</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Brand: wrydao | Model Name: H6 Pro | Surface Recommendation: Carpet Hard Floor Wood Tile | Special Feature: Advanced Custom Cleaning, Anti-Collision, Anti-Fall, Auto-Docking, Automatic Dust Collection, Pet Hair Pick Up | Color: Coral Black</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>wrydao</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0H2V9LVLF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>Robot Vacuum and Mop Self Emptying: 6000Pa Robotic Vacuum with Mapping, 90 Days Hands-Free Cleaning, LIDAR Navigation, Alexa/APP Control, 3-in-1 Robot Vacuum for Pet Hair Hard Floor Carpet Home</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>💨 360° LiDAR Navigation &amp; Home Mapping : H6 Pro robot vacuum is eqquipped with the most advanced LiDAR system, scan and identify complex home layouts at 360°, create highly detailed maps and supports multi-level mapping for smart navigation across different floors. Enjoy quick, accurate, and thorough cleaning in every corner of your home.
 🍀 90-Days Hands-Free Cleaning : The H6 Pro Robot Vacuum and Mop features a 3L large-capacity dust collection station, which can quickly dump dirt and dust into the dust bag while preventing clogging. Set your hands free and enjoy a fully automatic cleaning.
@@ -20374,505 +20018,256 @@
 💌 Worry-Free 2-Year Warranty &amp; Support ：Backed by 24/7 responsive support team, we offer a 2-year warranty and lifetime technical assistance, ensuring your perfect using experience from unboxing to everyday use.</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr">
+      <c r="J44" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0H2V9LVLF?psc=1</t>
         </is>
       </c>
-      <c r="K45" s="14" t="inlineStr">
+      <c r="K44" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/71DLRSID7BL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="L44" s="14" t="inlineStr">
         <is>
           <t>B0HH8NB97S</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr">
+      <c r="M44" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
-      <c r="N45" s="14" t="inlineStr">
+      <c r="N44" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O45" s="15">
+      <c r="O44" s="15">
         <v>22705</v>
       </c>
-      <c r="P45" s="15">
+      <c r="P44" s="15">
         <v>21158</v>
       </c>
-      <c r="Q45" s="16">
+      <c r="Q44" s="16">
         <v>0.51</v>
       </c>
-      <c r="R45" s="17" t="inlineStr">
+      <c r="R44" s="17" t="inlineStr">
         <is>
           <t>Robotic Vacuums</t>
         </is>
       </c>
-      <c r="S45" s="18" t="inlineStr">
+      <c r="S44" s="18" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T45" s="15">
+      <c r="T44" s="15">
         <v>260</v>
       </c>
-      <c r="U45" s="16"/>
-      <c r="V45" s="15">
+      <c r="U44" s="16"/>
+      <c r="V44" s="15">
         <v>62163</v>
       </c>
-      <c r="W45" s="15" t="inlineStr">
+      <c r="W44" s="15" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="X45" s="15">
+      <c r="X44" s="15">
         <v>159998</v>
       </c>
-      <c r="Y45" s="19">
+      <c r="Y44" s="19">
         <v>1</v>
       </c>
-      <c r="Z45" s="20">
+      <c r="Z44" s="20">
         <v>239.09</v>
       </c>
-      <c r="AA45" s="4">
+      <c r="AA44" s="4">
         <v>239.09</v>
       </c>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="15"/>
-      <c r="AD45" s="19">
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="15"/>
+      <c r="AD44" s="19">
         <v>44</v>
       </c>
-      <c r="AE45" s="15">
+      <c r="AE44" s="15">
         <v>2</v>
       </c>
-      <c r="AF45" s="21">
+      <c r="AF44" s="21">
         <v>4.9</v>
       </c>
-      <c r="AG45" s="22">
+      <c r="AG44" s="22">
         <v>0.0077</v>
       </c>
-      <c r="AH45" s="20">
+      <c r="AH44" s="20">
         <v>18.71</v>
       </c>
-      <c r="AI45" s="16">
+      <c r="AI44" s="16">
         <v>0.77</v>
       </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="13" t="inlineStr">
+      <c r="AJ44"/>
+      <c r="AK44" s="13" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="AL45" s="19">
+      <c r="AL44" s="19">
         <v>10</v>
       </c>
-      <c r="AM45" s="13" t="inlineStr">
+      <c r="AM44" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AN45" s="13" t="inlineStr">
+      <c r="AN44" s="13" t="inlineStr">
         <is>
           <t>6-8天</t>
         </is>
       </c>
-      <c r="AO45" s="13" t="inlineStr">
+      <c r="AO44" s="13" t="inlineStr">
         <is>
           <t>2天</t>
         </is>
       </c>
-      <c r="AP45" s="4"/>
-      <c r="AQ45" s="19">
+      <c r="AP44" s="4"/>
+      <c r="AQ44" s="19">
         <v>8</v>
       </c>
-      <c r="AR45" s="19">
+      <c r="AR44" s="19">
         <v>2</v>
       </c>
-      <c r="AS45" s="14" t="inlineStr">
+      <c r="AS44" s="14" t="inlineStr">
         <is>
           <t>HanHaoDongMoYuan20J-US</t>
         </is>
       </c>
-      <c r="AT45" s="13" t="inlineStr">
+      <c r="AT44" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU45" s="13" t="inlineStr">
+      <c r="AU44" s="13" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AV45" s="14" t="inlineStr">
+      <c r="AV44" s="14" t="inlineStr">
         <is>
           <t>西安市 陕西 710000 CN</t>
         </is>
       </c>
-      <c r="AW45" s="13" t="inlineStr">
+      <c r="AW44" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96</t>
         </is>
       </c>
-      <c r="AX45" s="13"/>
-      <c r="AY45" s="13" t="inlineStr">
+      <c r="AX44" s="13"/>
+      <c r="AY44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ45" s="13"/>
-      <c r="BA45" s="13"/>
-      <c r="BB45" s="13"/>
-      <c r="BC45" s="13" t="inlineStr">
+      <c r="AZ44" s="13"/>
+      <c r="BA44" s="13"/>
+      <c r="BB44" s="13"/>
+      <c r="BC44" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
-      <c r="BE45" s="13"/>
-      <c r="BF45" s="13"/>
-      <c r="BG45" s="13"/>
-      <c r="BH45" s="14"/>
-      <c r="BI45" s="23" t="inlineStr">
+      <c r="BD44" s="13"/>
+      <c r="BE44" s="13"/>
+      <c r="BF44" s="13"/>
+      <c r="BG44" s="13"/>
+      <c r="BH44" s="14"/>
+      <c r="BI44" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ45" s="23" t="inlineStr">
+      <c r="BJ44" s="23" t="inlineStr">
         <is>
           <t>7.88 pounds</t>
         </is>
       </c>
-      <c r="BK45" s="23" t="inlineStr">
+      <c r="BK44" s="23" t="inlineStr">
         <is>
           <t>3.57 kg</t>
         </is>
       </c>
-      <c r="BL45" s="23" t="inlineStr">
+      <c r="BL44" s="23" t="inlineStr">
         <is>
           <t>12.2"L x 12.2"W x 3.4"H</t>
         </is>
       </c>
-      <c r="BM45" s="23" t="inlineStr">
+      <c r="BM44" s="23" t="inlineStr">
         <is>
           <t>30.99 x 30.99 x 8.64 cm</t>
         </is>
       </c>
-      <c r="BN45" s="23" t="inlineStr">
+      <c r="BN44" s="23" t="inlineStr">
         <is>
           <t>7.9 pounds</t>
         </is>
       </c>
-      <c r="BO45" s="23" t="inlineStr">
+      <c r="BO44" s="23" t="inlineStr">
         <is>
           <t>3.58 kg</t>
         </is>
       </c>
-      <c r="BP45" s="23" t="inlineStr">
+      <c r="BP44" s="23" t="inlineStr">
         <is>
           <t>15 x 14.8 x 12.8 inches</t>
         </is>
       </c>
-      <c r="BQ45" s="23" t="inlineStr">
+      <c r="BQ44" s="23" t="inlineStr">
         <is>
           <t>38.10 x 37.59 x 32.51 cm</t>
         </is>
       </c>
-      <c r="BR45" s="13" t="inlineStr">
+      <c r="BR44" s="13" t="inlineStr">
         <is>
           <t>小号大件</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
-        <v>45</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>B0BCF8N3B4</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>Size: 33.8 Fl Oz (Pack of 1)</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>Brand: ECOVACS | Item Form: Liquid | Scent: no | Specific Uses For Product: Floor | Material Feature: Scented</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>ECOVACS</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>ECOVACS Multi-Surface Floor Cleaning Solution, Compatible with DEEBOT X11 OMNI Cyclone / X9 PRO OMNI / T80 OMNI / T50 PRO OMNI / N30 Series / N20 Series and all other Robot Vacuum Cleaners, 1L</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
-        <is>
-          <t>Compatible with DEEBOT X1 OMNI/X1 TURBO/ T10 OMNI
-Extraordinary cleaning performance on multiple surface
-One bottle (1L) lasts for 3 months
-Refresh your home with lasting clean scent.</t>
-        </is>
-      </c>
-      <c r="J46" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0BCF8N3B4?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="14" t="inlineStr">
-        <is>
-          <t>B0DNB8M7ZM</t>
-        </is>
-      </c>
-      <c r="M46" s="14" t="inlineStr">
-        <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N46" s="14" t="inlineStr">
-        <is>
-          <t>Industrial &amp; Scientific</t>
-        </is>
-      </c>
-      <c r="O46" s="15">
-        <v>2921</v>
-      </c>
-      <c r="P46" s="15">
-        <v>-647</v>
-      </c>
-      <c r="Q46" s="16">
-        <v>-0.22</v>
-      </c>
-      <c r="R46" s="17" t="inlineStr">
-        <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S46" s="18" t="inlineStr">
-        <is>
-          <t>6
-22</t>
-        </is>
-      </c>
-      <c r="T46" s="15">
-        <v>2102</v>
-      </c>
-      <c r="U46" s="16">
-        <v>-0.01</v>
-      </c>
-      <c r="V46" s="15">
-        <v>52529</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>24990</v>
-      </c>
-      <c r="Y46" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z46" s="20">
-        <v>24.99</v>
-      </c>
-      <c r="AA46" s="4"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="15">
-        <v>3</v>
-      </c>
-      <c r="AD46" s="19">
-        <v>1223</v>
-      </c>
-      <c r="AE46" s="15">
-        <v>30</v>
-      </c>
-      <c r="AF46" s="21">
-        <v>4.5</v>
-      </c>
-      <c r="AG46" s="22">
-        <v>0.0143</v>
-      </c>
-      <c r="AH46" s="20">
-        <v>6.48</v>
-      </c>
-      <c r="AI46" s="16">
-        <v>0.62</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="13" t="inlineStr">
-        <is>
-          <t>2023-02-17</t>
-        </is>
-      </c>
-      <c r="AL46" s="19">
-        <v>1319</v>
-      </c>
-      <c r="AM46" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN46" s="13" t="inlineStr">
-        <is>
-          <t>6天</t>
-        </is>
-      </c>
-      <c r="AO46" s="13" t="inlineStr">
-        <is>
-          <t>2天</t>
-        </is>
-      </c>
-      <c r="AP46" s="4"/>
-      <c r="AQ46" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR46" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS46" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT46" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
-      <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ46" s="13"/>
-      <c r="BA46" s="13"/>
-      <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="13"/>
-      <c r="BE46" s="13"/>
-      <c r="BF46" s="13"/>
-      <c r="BG46" s="13"/>
-      <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ46" s="23" t="inlineStr">
-        <is>
-          <t>1.22 kg</t>
-        </is>
-      </c>
-      <c r="BK46" s="23" t="inlineStr">
-        <is>
-          <t>1.22 kg</t>
-        </is>
-      </c>
-      <c r="BL46" s="23" t="inlineStr">
-        <is>
-          <t>3.5 x 3.5 x 9.7 inches</t>
-        </is>
-      </c>
-      <c r="BM46" s="23" t="inlineStr">
-        <is>
-          <t>8.89 x 8.89 x 24.64 cm</t>
-        </is>
-      </c>
-      <c r="BN46" s="23" t="inlineStr">
-        <is>
-          <t>2.62 pounds</t>
-        </is>
-      </c>
-      <c r="BO46" s="23" t="inlineStr">
-        <is>
-          <t>1.19 kg</t>
-        </is>
-      </c>
-      <c r="BP46" s="23" t="inlineStr">
-        <is>
-          <t>9.7 x 3.5 x 3.5 inches</t>
-        </is>
-      </c>
-      <c r="BQ46" s="23" t="inlineStr">
-        <is>
-          <t>24.64 x 8.89 x 8.89 cm</t>
-        </is>
-      </c>
-      <c r="BR46" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13">
-        <v>46</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14" t="inlineStr">
+    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>44</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>B0HF7K2ZKS</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>Color: Black</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Brand: XIEBro | Model Name: E8S Robot Vacuum | Surface Recommendation: Hard Floor,Low Pile Carpet, Wood Floor, Tile Floor | Special Feature: Anti-Fall, Edge Cleaning, Pet Hair Pick Up, Scheduling, Simultaneous Vacuuming &amp; Mopping | Color: Black</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>XIEBro</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0HF7K2ZKS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>Robot Vacuum and Mop, 6500Pa Suction, 2 in 1 Robotic Vacuum with Gyro Inertial Navigation, 200 Min Runtime, App/Remote/Voice Control, Ideal for Pet Hair, Hard Floor, Carpet</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>🗺️🤸【Upgraded Gyro Navigation for Systematic Cleaning】E8S features an enhanced gyroscope and inertial navigation system, eliminating the random collisions and incomplete coverage common in traditional models. It cleans in a precise, orderly zigzag cleaning path, ensuring more systematic coverage and a larger cleaning area. Equipped with all-around infrared sensors, it accurately detects walls, stairs, and furniture, combined with 15° obstacle-crossing ability, effortlessly navigating different floor heights while avoiding collisions and falls.
 🌀🔄【6500Pa Powerful Suction for Deep Cleaning in Any Scenario】Powered by a robust digital motor, the E8S delivers a maximum 6500Pa hurricane-level suction, instantly lifting debris and pet hair embedded deep in carpets, effortlessly handling whole-home cleaning challenges. It offers four suction modes: Eco (800Pa), Standard (1600Pa), Strong (3000Pa), and Max (6500Pa), along with automatic carpet boost, seamlessly adapting to various floor types like tile, hardwood, carpet, and marble. Whether it's daily dust, stubborn stains, or heavy pet hair during shedding season, one tap handles it all, keeping your home consistently spotless.
@@ -20883,264 +20278,264 @@
 📦🤖【What You Get】You will receive: E8S Robot Vacuum, remote control (with 2 AAA batteries), charging dock, power adapter, water tank, dustbin, 4 side brushes, and user manual. We offer professional customer support and a 12-month warranty, ensuring a worry-free purchase and peace of mind during use.</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0HF7K2ZKS?psc=1</t>
         </is>
       </c>
-      <c r="K47" s="14" t="inlineStr">
+      <c r="K45" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="L45" s="14" t="inlineStr">
         <is>
           <t>B0HJXGHYVB</t>
         </is>
       </c>
-      <c r="M47" s="14" t="inlineStr">
+      <c r="M45" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
-      <c r="N47" s="14" t="inlineStr">
+      <c r="N45" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O47" s="15">
+      <c r="O45" s="15">
         <v>29244</v>
       </c>
-      <c r="P47" s="15">
+      <c r="P45" s="15">
         <v>34292</v>
       </c>
-      <c r="Q47" s="16">
+      <c r="Q45" s="16">
         <v>0.56</v>
       </c>
-      <c r="R47" s="17" t="inlineStr">
+      <c r="R45" s="17" t="inlineStr">
         <is>
           <t>Robotic Vacuums</t>
         </is>
       </c>
-      <c r="S47" s="18" t="inlineStr">
+      <c r="S45" s="18" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T47" s="15">
+      <c r="T45" s="15">
         <v>348</v>
       </c>
-      <c r="U47" s="16"/>
-      <c r="V47" s="15">
+      <c r="U45" s="16"/>
+      <c r="V45" s="15">
         <v>52197</v>
       </c>
-      <c r="W47" s="15" t="inlineStr">
+      <c r="W45" s="15" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="X47" s="15">
+      <c r="X45" s="15">
         <v>131412</v>
       </c>
-      <c r="Y47" s="19">
+      <c r="Y45" s="19">
         <v>1</v>
       </c>
-      <c r="Z47" s="20">
+      <c r="Z45" s="20">
         <v>149.99</v>
       </c>
-      <c r="AA47" s="4">
+      <c r="AA45" s="4">
         <v>149.99</v>
       </c>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="15"/>
-      <c r="AD47" s="19">
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="15"/>
+      <c r="AD45" s="19">
         <v>19</v>
       </c>
-      <c r="AE47" s="15">
+      <c r="AE45" s="15">
         <v>0</v>
       </c>
-      <c r="AF47" s="21">
+      <c r="AF45" s="21">
         <v>4.6</v>
       </c>
-      <c r="AG47" s="22">
+      <c r="AG45" s="22">
         <v>0</v>
       </c>
-      <c r="AH47" s="20">
+      <c r="AH45" s="20">
         <v>9</v>
       </c>
-      <c r="AI47" s="16">
+      <c r="AI45" s="16">
         <v>0.79</v>
       </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="13" t="inlineStr">
+      <c r="AJ45"/>
+      <c r="AK45" s="13" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="AL47" s="19">
+      <c r="AL45" s="19">
         <v>33</v>
       </c>
-      <c r="AM47" s="13" t="inlineStr">
+      <c r="AM45" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AN47" s="13" t="inlineStr">
+      <c r="AN45" s="13" t="inlineStr">
         <is>
           <t>6天</t>
         </is>
       </c>
-      <c r="AO47" s="13" t="inlineStr">
+      <c r="AO45" s="13" t="inlineStr">
         <is>
           <t>2天</t>
         </is>
       </c>
-      <c r="AP47" s="4"/>
-      <c r="AQ47" s="19">
+      <c r="AP45" s="4"/>
+      <c r="AQ45" s="19">
         <v>8</v>
       </c>
-      <c r="AR47" s="19">
+      <c r="AR45" s="19">
         <v>1</v>
       </c>
-      <c r="AS47" s="14" t="inlineStr">
+      <c r="AS45" s="14" t="inlineStr">
         <is>
           <t>zchenymei</t>
         </is>
       </c>
-      <c r="AT47" s="13" t="inlineStr">
+      <c r="AT45" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU47" s="13" t="inlineStr">
+      <c r="AU45" s="13" t="inlineStr">
         <is>
           <t>CN(HK)</t>
         </is>
       </c>
-      <c r="AV47" s="14" t="inlineStr">
+      <c r="AV45" s="14" t="inlineStr">
         <is>
           <t>KOWLOON HONGKONG 999077 HK</t>
         </is>
       </c>
-      <c r="AW47" s="13" t="inlineStr">
+      <c r="AW45" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN</t>
         </is>
       </c>
-      <c r="AX47" s="13"/>
-      <c r="AY47" s="13" t="inlineStr">
+      <c r="AX45" s="13"/>
+      <c r="AY45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ47" s="13"/>
-      <c r="BA47" s="13"/>
-      <c r="BB47" s="13"/>
-      <c r="BC47" s="13" t="inlineStr">
+      <c r="AZ45" s="13"/>
+      <c r="BA45" s="13"/>
+      <c r="BB45" s="13"/>
+      <c r="BC45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="13" t="inlineStr">
+      <c r="BD45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE47" s="13"/>
-      <c r="BF47" s="13" t="inlineStr">
+      <c r="BE45" s="13"/>
+      <c r="BF45" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG47" s="13"/>
-      <c r="BH47" s="14"/>
-      <c r="BI47" s="23" t="inlineStr">
+      <c r="BG45" s="13"/>
+      <c r="BH45" s="14"/>
+      <c r="BI45" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ47" s="23" t="inlineStr">
+      <c r="BJ45" s="23" t="inlineStr">
         <is>
           <t>7.04 pounds</t>
         </is>
       </c>
-      <c r="BK47" s="23" t="inlineStr">
+      <c r="BK45" s="23" t="inlineStr">
         <is>
           <t>3.19 kg</t>
         </is>
       </c>
-      <c r="BL47" s="23" t="inlineStr">
+      <c r="BL45" s="23" t="inlineStr">
         <is>
           <t>11.81"L x 11.81"W x 2.95"H</t>
         </is>
       </c>
-      <c r="BM47" s="23" t="inlineStr">
+      <c r="BM45" s="23" t="inlineStr">
         <is>
           <t>30.00 x 30.00 x 7.49 cm</t>
         </is>
       </c>
-      <c r="BN47" s="23" t="inlineStr">
+      <c r="BN45" s="23" t="inlineStr">
         <is>
           <t>7.05 pounds</t>
         </is>
       </c>
-      <c r="BO47" s="23" t="inlineStr">
+      <c r="BO45" s="23" t="inlineStr">
         <is>
           <t>3.20 kg</t>
         </is>
       </c>
-      <c r="BP47" s="23" t="inlineStr">
+      <c r="BP45" s="23" t="inlineStr">
         <is>
           <t>16.3 x 12.9 x 4.3 inches</t>
         </is>
       </c>
-      <c r="BQ47" s="23" t="inlineStr">
+      <c r="BQ45" s="23" t="inlineStr">
         <is>
           <t>41.40 x 32.77 x 10.92 cm</t>
         </is>
       </c>
-      <c r="BR47" s="13" t="inlineStr">
+      <c r="BR45" s="13" t="inlineStr">
         <is>
           <t>大号标准尺寸</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
-        <v>47</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14" t="inlineStr">
+    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13">
+        <v>45</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>B0GSH62CFF</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>Color: Black New</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Brand: iRobot | Model Name: 705X Combo Robot | Surface Recommendation: Carpet &amp; Hard Floor | Special Feature: LiDAR Navigation | Color: Black New</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>iRobot</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B0GSH62CFF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>iRobot Roomba 705X Robot Vacuum &amp; Mop Combo, 175x More Suction, Extending Self-Cleaning Roller Mop, Multifunction Dock, 75 Day Self-Emptying, Hot Wash/Dry, AI Obstacle Avoidance, Ideal for Pet Hair</t>
         </is>
       </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>THE ULTIMATE HANDS‑FREE CLEAN FOR REAL HOMES. The most advanced Roomba yet— the Roomba Max 705X is designed to clean every room without stopping, adjusting automatically as it moves from hard floors to carpet, vacuuming and mopping in one seamless pass, and navigating effortlessly around everyday obstacles.
 THE ONLY ROOMBA THAT CLEANS ITSELF WHILE IT CLEANS YOUR HOME. The self‑cleaning roller mop continuously washes itself during use, extends to reach edges and corners, and protects carpets with a built‑in cover—so wet and dry messes never mix.
@@ -21153,268 +20548,268 @@
 VOICE‑ACTIVATED, EFFORTLESS CLEANING. Just ask Alexa, Siri, or Google Assistant* to vacuum the living room, combo‑clean the kitchen, or tidy up near the couch—no scheduling, no setup, no stress. *Works with Alexa, Siri, and Google Assistant-enabled devices</t>
         </is>
       </c>
-      <c r="J48" s="14" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0GSH62CFF?psc=1</t>
         </is>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/71pXZvcdNQL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L48" s="14" t="inlineStr">
+      <c r="L46" s="14" t="inlineStr">
         <is>
           <t>B0H6KJWTHQ</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr">
+      <c r="M46" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
-      <c r="N48" s="14" t="inlineStr">
+      <c r="N46" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O48" s="15">
+      <c r="O46" s="15">
         <v>37257</v>
       </c>
-      <c r="P48" s="15">
+      <c r="P46" s="15">
         <v>351597</v>
       </c>
-      <c r="Q48" s="16">
+      <c r="Q46" s="16">
         <v>0.56</v>
       </c>
-      <c r="R48" s="17" t="inlineStr">
+      <c r="R46" s="17" t="inlineStr">
         <is>
           <t>Robotic Vacuums</t>
         </is>
       </c>
-      <c r="S48" s="18" t="inlineStr">
+      <c r="S46" s="18" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="T48" s="15">
+      <c r="T46" s="15">
         <v>67</v>
       </c>
-      <c r="U48" s="16">
+      <c r="U46" s="16">
         <v>-0.81</v>
       </c>
-      <c r="V48" s="15">
+      <c r="V46" s="15">
         <v>46899</v>
       </c>
-      <c r="W48" s="15" t="inlineStr">
+      <c r="W46" s="15" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="X48" s="15"/>
-      <c r="Y48" s="19">
+      <c r="X46" s="15"/>
+      <c r="Y46" s="19">
         <v>2</v>
       </c>
-      <c r="Z48" s="20">
+      <c r="Z46" s="20">
         <v>699.99</v>
       </c>
-      <c r="AA48" s="4">
+      <c r="AA46" s="4">
         <v>699.99</v>
       </c>
-      <c r="AB48" s="1"/>
-      <c r="AC48" s="15"/>
-      <c r="AD48" s="19">
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="15"/>
+      <c r="AD46" s="19">
         <v>13223</v>
       </c>
-      <c r="AE48" s="15">
+      <c r="AE46" s="15">
         <v>15</v>
       </c>
-      <c r="AF48" s="21">
+      <c r="AF46" s="21">
         <v>4.3</v>
       </c>
-      <c r="AG48" s="22">
+      <c r="AG46" s="22">
         <v>0.22390000000000002</v>
       </c>
-      <c r="AH48" s="20">
+      <c r="AH46" s="20">
         <v>39.51</v>
       </c>
-      <c r="AI48" s="16">
+      <c r="AI46" s="16">
         <v>0.79</v>
       </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="13" t="inlineStr">
+      <c r="AJ46"/>
+      <c r="AK46" s="13" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AL48" s="19">
+      <c r="AL46" s="19">
         <v>194</v>
       </c>
-      <c r="AM48" s="13" t="inlineStr">
+      <c r="AM46" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AN48" s="13" t="inlineStr">
+      <c r="AN46" s="13" t="inlineStr">
         <is>
           <t>6天</t>
         </is>
       </c>
-      <c r="AO48" s="13" t="inlineStr">
+      <c r="AO46" s="13" t="inlineStr">
         <is>
           <t>2天</t>
         </is>
       </c>
-      <c r="AP48" s="4"/>
-      <c r="AQ48" s="19">
+      <c r="AP46" s="4"/>
+      <c r="AQ46" s="19">
         <v>10</v>
       </c>
-      <c r="AR48" s="19">
+      <c r="AR46" s="19">
         <v>5</v>
       </c>
-      <c r="AS48" s="14" t="inlineStr">
+      <c r="AS46" s="14" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="AT48" s="13" t="inlineStr">
+      <c r="AT46" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AU48" s="13" t="inlineStr">
+      <c r="AU46" s="13" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="AV48" s="14" t="inlineStr">
+      <c r="AV46" s="14" t="inlineStr">
         <is>
           <t>AZ 85032 US</t>
         </is>
       </c>
-      <c r="AW48" s="13" t="inlineStr">
+      <c r="AW46" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P0ZBGEDS6RH6</t>
         </is>
       </c>
-      <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
+      <c r="AX46" s="13"/>
+      <c r="AY46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ48" s="13"/>
-      <c r="BA48" s="13"/>
-      <c r="BB48" s="13"/>
-      <c r="BC48" s="13" t="inlineStr">
+      <c r="AZ46" s="13"/>
+      <c r="BA46" s="13"/>
+      <c r="BB46" s="13"/>
+      <c r="BC46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD48" s="13" t="inlineStr">
+      <c r="BD46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE48" s="13"/>
-      <c r="BF48" s="13" t="inlineStr">
+      <c r="BE46" s="13"/>
+      <c r="BF46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG48" s="13"/>
-      <c r="BH48" s="14" t="inlineStr">
+      <c r="BG46" s="13"/>
+      <c r="BH46" s="14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BI48" s="23" t="inlineStr">
+      <c r="BI46" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ48" s="23" t="inlineStr">
+      <c r="BJ46" s="23" t="inlineStr">
         <is>
           <t>40.7 pounds</t>
         </is>
       </c>
-      <c r="BK48" s="23" t="inlineStr">
+      <c r="BK46" s="23" t="inlineStr">
         <is>
           <t>18.46 kg</t>
         </is>
       </c>
-      <c r="BL48" s="23" t="inlineStr">
+      <c r="BL46" s="23" t="inlineStr">
         <is>
           <t>14.6"L x 14.7"W x 4.1"H</t>
         </is>
       </c>
-      <c r="BM48" s="23" t="inlineStr">
+      <c r="BM46" s="23" t="inlineStr">
         <is>
           <t>37.08 x 37.34 x 10.41 cm</t>
         </is>
       </c>
-      <c r="BN48" s="23" t="inlineStr">
+      <c r="BN46" s="23" t="inlineStr">
         <is>
           <t>40.78 pounds</t>
         </is>
       </c>
-      <c r="BO48" s="23" t="inlineStr">
+      <c r="BO46" s="23" t="inlineStr">
         <is>
           <t>18.50 kg</t>
         </is>
       </c>
-      <c r="BP48" s="23" t="inlineStr">
+      <c r="BP46" s="23" t="inlineStr">
         <is>
           <t>20 x 19.8 x 18 inches</t>
         </is>
       </c>
-      <c r="BQ48" s="23" t="inlineStr">
+      <c r="BQ46" s="23" t="inlineStr">
         <is>
           <t>50.80 x 50.29 x 45.72 cm</t>
         </is>
       </c>
-      <c r="BR48" s="13" t="inlineStr">
+      <c r="BR46" s="13" t="inlineStr">
         <is>
           <t>超大尺寸：50 到 70 磅（不含 50 磅）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="13">
-        <v>48</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14" t="inlineStr">
+    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13">
+        <v>46</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>B0HFJCMP9T</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Color: Light Black</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>Brand: wrydao | Model Name: H22 | Surface Recommendation: wood, carpet, tiles | Special Feature: Upgraded Intelligent Navigation, Obstacle Avoidance, Carpet Auto-Boost, 5 Cleaning Modes, App/Alexa/Voice Control, 120mins Runtime, Self-charging, Tangle-Free, Ultra-Slim Design, 2-Year Worry-Free Warranty | Color: Light Black</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>wrydao</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJCMP9T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>Robot Vacuum and Mop Combo, 5000Pa Self-Charging Robotic Vacuum cleaner with Alexa &amp; App Control, 3-in-1 Robot Vacuum with Smart Obstacle Avoidance, Ideal for Pet Hair, Carpet and Floors, Slim, Quiet</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Sweep, vacuum, and mop 3-in-1: This robot vacuum comes with an integrated dustbin-water tank combo, allowing it to vacuum and mop simultaneously while picking up even the finest particles that regular sweeping might miss. With a 250ml dustbin plus a 200ml water tank, it tackles large-area cleaning with ease.
 5000Pa Strong Suction &amp; Carpet Auto-Boost: Equipped with a robust 5000Pa suction and an automatic carpet boost feature, this robot vacuum powers through everyday messes effortlessly. On carpets, the suction automatically intensifies to lift embedded pet hair, crumbs, and stubborn debris from carpets – delivering a deep clean that leaves no dirt behind.
@@ -21425,246 +20820,246 @@
 2-Year Worry-Free Warranty and Support: We provide a 2‑year warranty and lifelong technical assistance, ensuring a flawless experience from the moment you open the box through years of daily operation.</t>
         </is>
       </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0HFJCMP9T?psc=1</t>
         </is>
       </c>
-      <c r="K49" s="14" t="inlineStr">
+      <c r="K47" s="14" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L49" s="14" t="inlineStr">
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>B0HK45FHVF</t>
         </is>
       </c>
-      <c r="M49" s="14" t="inlineStr">
+      <c r="M47" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
-      <c r="N49" s="14" t="inlineStr">
+      <c r="N47" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O49" s="15">
+      <c r="O47" s="15">
         <v>35926</v>
       </c>
-      <c r="P49" s="15">
+      <c r="P47" s="15">
         <v>1086244</v>
       </c>
-      <c r="Q49" s="16">
+      <c r="Q47" s="16">
         <v>0.97</v>
       </c>
-      <c r="R49" s="17" t="inlineStr">
+      <c r="R47" s="17" t="inlineStr">
         <is>
           <t>Robotic Vacuums</t>
         </is>
       </c>
-      <c r="S49" s="18" t="inlineStr">
+      <c r="S47" s="18" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="T49" s="15">
+      <c r="T47" s="15">
         <v>224</v>
       </c>
-      <c r="U49" s="16">
+      <c r="U47" s="16">
         <v>14.09</v>
       </c>
-      <c r="V49" s="15">
+      <c r="V47" s="15">
         <v>22398</v>
       </c>
-      <c r="W49" s="15"/>
-      <c r="X49" s="15"/>
-      <c r="Y49" s="19">
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
+      <c r="Y47" s="19">
         <v>4</v>
       </c>
-      <c r="Z49" s="20">
+      <c r="Z47" s="20">
         <v>99.99</v>
       </c>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="1"/>
-      <c r="AC49" s="15"/>
-      <c r="AD49" s="19">
+      <c r="AA47" s="4"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="15"/>
+      <c r="AD47" s="19">
         <v>28</v>
       </c>
-      <c r="AE49" s="15">
+      <c r="AE47" s="15">
         <v>16</v>
       </c>
-      <c r="AF49" s="21">
+      <c r="AF47" s="21">
         <v>5</v>
       </c>
-      <c r="AG49" s="22">
+      <c r="AG47" s="22">
         <v>0.07139999999999999</v>
       </c>
-      <c r="AH49" s="20">
+      <c r="AH47" s="20">
         <v>9.17</v>
       </c>
-      <c r="AI49" s="16">
+      <c r="AI47" s="16">
         <v>0.76</v>
       </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
+      <c r="AJ47"/>
+      <c r="AK47" s="13" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="AL49" s="19">
+      <c r="AL47" s="19">
         <v>13</v>
       </c>
-      <c r="AM49" s="13" t="inlineStr">
+      <c r="AM47" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AN49" s="13" t="inlineStr">
+      <c r="AN47" s="13" t="inlineStr">
         <is>
           <t>13-23天</t>
         </is>
       </c>
-      <c r="AO49" s="13"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="19">
+      <c r="AO47" s="13"/>
+      <c r="AP47" s="4"/>
+      <c r="AQ47" s="19">
         <v>10</v>
       </c>
-      <c r="AR49" s="19">
+      <c r="AR47" s="19">
         <v>1</v>
       </c>
-      <c r="AS49" s="14" t="inlineStr">
+      <c r="AS47" s="14" t="inlineStr">
         <is>
           <t>Yqmizmz-us</t>
         </is>
       </c>
-      <c r="AT49" s="13" t="inlineStr">
+      <c r="AT47" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU49" s="13" t="inlineStr">
+      <c r="AU47" s="13" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AV49" s="14" t="inlineStr">
+      <c r="AV47" s="14" t="inlineStr">
         <is>
           <t>襄阳市 湖北省 441199 CN</t>
         </is>
       </c>
-      <c r="AW49" s="13" t="inlineStr">
+      <c r="AW47" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PGFDS4HWDNZG</t>
         </is>
       </c>
-      <c r="AX49" s="13"/>
-      <c r="AY49" s="13" t="inlineStr">
+      <c r="AX47" s="13"/>
+      <c r="AY47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ49" s="13"/>
-      <c r="BA49" s="13"/>
-      <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
+      <c r="AZ47" s="13"/>
+      <c r="BA47" s="13"/>
+      <c r="BB47" s="13"/>
+      <c r="BC47" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13"/>
-      <c r="BE49" s="13"/>
-      <c r="BF49" s="13"/>
-      <c r="BG49" s="13"/>
-      <c r="BH49" s="14"/>
-      <c r="BI49" s="23" t="inlineStr">
+      <c r="BD47" s="13"/>
+      <c r="BE47" s="13"/>
+      <c r="BF47" s="13"/>
+      <c r="BG47" s="13"/>
+      <c r="BH47" s="14"/>
+      <c r="BI47" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ49" s="23" t="inlineStr">
+      <c r="BJ47" s="23" t="inlineStr">
         <is>
           <t>7.4 pounds</t>
         </is>
       </c>
-      <c r="BK49" s="23" t="inlineStr">
+      <c r="BK47" s="23" t="inlineStr">
         <is>
           <t>3.36 kg</t>
         </is>
       </c>
-      <c r="BL49" s="23" t="inlineStr">
+      <c r="BL47" s="23" t="inlineStr">
         <is>
           <t>12.2"L x 12.2"W x 3.15"H</t>
         </is>
       </c>
-      <c r="BM49" s="23" t="inlineStr">
+      <c r="BM47" s="23" t="inlineStr">
         <is>
           <t>30.99 x 30.99 x 8.00 cm</t>
         </is>
       </c>
-      <c r="BN49" s="23" t="inlineStr">
+      <c r="BN47" s="23" t="inlineStr">
         <is>
           <t>7.16 pounds</t>
         </is>
       </c>
-      <c r="BO49" s="23" t="inlineStr">
+      <c r="BO47" s="23" t="inlineStr">
         <is>
           <t>3.25 kg</t>
         </is>
       </c>
-      <c r="BP49" s="23" t="inlineStr">
+      <c r="BP47" s="23" t="inlineStr">
         <is>
           <t>16.5 x 13.7 x 4.6 inches</t>
         </is>
       </c>
-      <c r="BQ49" s="23" t="inlineStr">
+      <c r="BQ47" s="23" t="inlineStr">
         <is>
           <t>41.91 x 34.80 x 11.68 cm</t>
         </is>
       </c>
-      <c r="BR49" s="13" t="inlineStr">
+      <c r="BR47" s="13" t="inlineStr">
         <is>
           <t>大号标准尺寸</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
+    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
+        <v>47</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>B07BRVNXZW</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Style: Side Brush - Type C | Size: side brush- White</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>Brand: roborock | Color: Side Brushes (White) | Handle Material: Plastic | Product Dimensions: 2.36"L x 2.36"W x 0.39"H | Material: Nylon, Rubber</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F48" s="14" t="inlineStr">
         <is>
           <t>roborock</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
+      <c r="G48" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>roborock Side Brushes Replacement (2 Pieces) for S8 Pro Ultra, S7 Max Ultra, Q Revo, Series of S7 MaxV/S7/Q7Max/Q8 Max/S8/Q7/Q5/S6/S5/S4/E5/E4/E3/E2 Robot Vacuum Cleaner, White</t>
         </is>
       </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>This replacement side brushes for robotic vacuum sweeps the edges of rooms, flicking dust into the suction system path.
 Crafted from durable nylon, our side brush set accessories offer a thorough cleaning experience without leaving any marks on furniture or walls.
@@ -21674,254 +21069,254 @@
 Note: To protect your robot vacuum machine and extend its lifespan, please purchase replacement parts from Roborock store. If you have any questions, please feel free to contact us.</t>
         </is>
       </c>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="J48" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B07BRVNXZW?psc=1</t>
         </is>
       </c>
-      <c r="K50" s="14" t="inlineStr">
+      <c r="K48" s="14" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg</t>
         </is>
       </c>
-      <c r="L50" s="14" t="inlineStr">
+      <c r="L48" s="14" t="inlineStr">
         <is>
           <t>B0GHNN4HT7</t>
         </is>
       </c>
-      <c r="M50" s="14" t="inlineStr">
+      <c r="M48" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
-      <c r="N50" s="14" t="inlineStr">
+      <c r="N48" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O50" s="15">
+      <c r="O48" s="15">
         <v>30306</v>
       </c>
-      <c r="P50" s="15">
+      <c r="P48" s="15">
         <v>-2368</v>
       </c>
-      <c r="Q50" s="16">
+      <c r="Q48" s="16">
         <v>-0.08</v>
       </c>
-      <c r="R50" s="17" t="inlineStr">
+      <c r="R48" s="17" t="inlineStr">
         <is>
           <t>Robotic Vacuums</t>
         </is>
       </c>
-      <c r="S50" s="18" t="inlineStr">
+      <c r="S48" s="18" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="T50" s="15">
+      <c r="T48" s="15">
         <v>1118</v>
       </c>
-      <c r="U50" s="16">
+      <c r="U48" s="16">
         <v>0.34</v>
       </c>
-      <c r="V50" s="15">
+      <c r="V48" s="15">
         <v>17877</v>
       </c>
-      <c r="W50" s="15" t="inlineStr">
+      <c r="W48" s="15" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="X50" s="15">
+      <c r="X48" s="15">
         <v>7995</v>
       </c>
-      <c r="Y50" s="19">
+      <c r="Y48" s="19">
         <v>2</v>
       </c>
-      <c r="Z50" s="20">
+      <c r="Z48" s="20">
         <v>15.99</v>
       </c>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="15">
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="15">
         <v>23</v>
       </c>
-      <c r="AD50" s="19">
+      <c r="AD48" s="19">
         <v>868</v>
       </c>
-      <c r="AE50" s="15">
+      <c r="AE48" s="15">
         <v>11</v>
       </c>
-      <c r="AF50" s="21">
+      <c r="AF48" s="21">
         <v>4.7</v>
       </c>
-      <c r="AG50" s="22">
+      <c r="AG48" s="22">
         <v>0.0098</v>
       </c>
-      <c r="AH50" s="20">
+      <c r="AH48" s="20">
         <v>4.09</v>
       </c>
-      <c r="AI50" s="16">
+      <c r="AI48" s="16">
         <v>0.59</v>
       </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
+      <c r="AJ48"/>
+      <c r="AK48" s="13" t="inlineStr">
         <is>
           <t>2018-05-08</t>
         </is>
       </c>
-      <c r="AL50" s="19">
+      <c r="AL48" s="19">
         <v>3065</v>
       </c>
-      <c r="AM50" s="13" t="inlineStr">
+      <c r="AM48" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AN50" s="13" t="inlineStr">
+      <c r="AN48" s="13" t="inlineStr">
         <is>
           <t>6天</t>
         </is>
       </c>
-      <c r="AO50" s="13" t="inlineStr">
+      <c r="AO48" s="13" t="inlineStr">
         <is>
           <t>2天</t>
         </is>
       </c>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="19">
+      <c r="AP48" s="4"/>
+      <c r="AQ48" s="19">
         <v>10</v>
       </c>
-      <c r="AR50" s="19">
+      <c r="AR48" s="19">
         <v>1</v>
       </c>
-      <c r="AS50" s="14" t="inlineStr">
+      <c r="AS48" s="14" t="inlineStr">
         <is>
           <t>Roborock Technology Co. Ltd</t>
         </is>
       </c>
-      <c r="AT50" s="13" t="inlineStr">
+      <c r="AT48" s="13" t="inlineStr">
         <is>
           <t>FBA</t>
         </is>
       </c>
-      <c r="AU50" s="13" t="inlineStr">
+      <c r="AU48" s="13" t="inlineStr">
         <is>
           <t>CN(HK)</t>
         </is>
       </c>
-      <c r="AV50" s="14" t="inlineStr">
+      <c r="AV48" s="14" t="inlineStr">
         <is>
           <t>SHEUNG WAN HK 999077 HK</t>
         </is>
       </c>
-      <c r="AW50" s="13" t="inlineStr">
+      <c r="AW48" s="13" t="inlineStr">
         <is>
           <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH</t>
         </is>
       </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
+      <c r="AX48" s="13"/>
+      <c r="AY48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
+      <c r="AZ48" s="13"/>
+      <c r="BA48" s="13"/>
+      <c r="BB48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
+      <c r="BD48" s="13"/>
+      <c r="BE48" s="13"/>
+      <c r="BF48" s="13"/>
+      <c r="BG48" s="13"/>
+      <c r="BH48" s="14"/>
+      <c r="BI48" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ50" s="23" t="inlineStr">
+      <c r="BJ48" s="23" t="inlineStr">
         <is>
           <t>1.8 ounces</t>
         </is>
       </c>
-      <c r="BK50" s="23" t="inlineStr">
+      <c r="BK48" s="23" t="inlineStr">
         <is>
           <t>51.03 g</t>
         </is>
       </c>
-      <c r="BL50" s="23" t="inlineStr">
+      <c r="BL48" s="23" t="inlineStr">
         <is>
           <t>2.36"L x 2.36"W x 0.39"H</t>
         </is>
       </c>
-      <c r="BM50" s="23" t="inlineStr">
+      <c r="BM48" s="23" t="inlineStr">
         <is>
           <t>5.99 x 5.99 x 0.99 cm</t>
         </is>
       </c>
-      <c r="BN50" s="23" t="inlineStr">
+      <c r="BN48" s="23" t="inlineStr">
         <is>
           <t>0.11 pounds</t>
         </is>
       </c>
-      <c r="BO50" s="23" t="inlineStr">
+      <c r="BO48" s="23" t="inlineStr">
         <is>
           <t>49.90 g</t>
         </is>
       </c>
-      <c r="BP50" s="23" t="inlineStr">
+      <c r="BP48" s="23" t="inlineStr">
         <is>
           <t>4.6 x 4.6 x 2 inches</t>
         </is>
       </c>
-      <c r="BQ50" s="23" t="inlineStr">
+      <c r="BQ48" s="23" t="inlineStr">
         <is>
           <t>11.68 x 11.68 x 5.08 cm</t>
         </is>
       </c>
-      <c r="BR50" s="13" t="inlineStr">
+      <c r="BR48" s="13" t="inlineStr">
         <is>
           <t>大号标准尺寸</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
+    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>48</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>B07KL93JBN</t>
         </is>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="D49" s="14"/>
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>Brand: iRobot | Model Name: 4636429 | Surface Recommendation: wall | Special Feature: Bagless | Color: Black</t>
         </is>
       </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="F49" s="14" t="inlineStr">
         <is>
           <t>iRobot</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
+      <c r="G49" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07KL93JBN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>iRobot Roomba Authentic Replacement Parts - Dual Mode Virtual Wall Barrier Compatible with Roomba 600 700 800 900 Series, Black - 4636429</t>
         </is>
       </c>
-      <c r="I51" s="14" t="inlineStr">
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>1-pack Dual Mode Virtual Wall Barrier gives you greater control over where your robot cleans
 Virtual Wall mode keeps your robot in the rooms you want cleaned and out of the ones you don't
@@ -21931,209 +21326,209 @@
 Compatible with all Roomba 500, 600, 700, 800 and 900 Series Robots and Scooba 400 Series Robots</t>
         </is>
       </c>
-      <c r="J51" s="14" t="inlineStr">
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B07KL93JBN?psc=1</t>
         </is>
       </c>
-      <c r="K51" s="14" t="inlineStr">
+      <c r="K49" s="14" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/31fAsdCfw7L._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L51" s="14" t="inlineStr">
+      <c r="L49" s="14" t="inlineStr">
         <is>
           <t>B07KL93JBN</t>
         </is>
       </c>
-      <c r="M51" s="14" t="inlineStr">
+      <c r="M49" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
-      <c r="N51" s="14" t="inlineStr">
+      <c r="N49" s="14" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="O51" s="15">
+      <c r="O49" s="15">
         <v>50549</v>
       </c>
-      <c r="P51" s="15">
+      <c r="P49" s="15">
         <v>-236767</v>
       </c>
-      <c r="Q51" s="16">
+      <c r="Q49" s="16">
         <v>-0.81</v>
       </c>
-      <c r="R51" s="17" t="inlineStr">
+      <c r="R49" s="17" t="inlineStr">
         <is>
           <t>Robotic Vacuums</t>
         </is>
       </c>
-      <c r="S51" s="18" t="inlineStr">
+      <c r="S49" s="18" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="T51" s="15">
+      <c r="T49" s="15">
         <v>210</v>
       </c>
-      <c r="U51" s="16">
+      <c r="U49" s="16">
         <v>-0.25</v>
       </c>
-      <c r="V51" s="15">
+      <c r="V49" s="15">
         <v>1716</v>
       </c>
-      <c r="W51" s="15" t="inlineStr">
+      <c r="W49" s="15" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="X51" s="15">
+      <c r="X49" s="15">
         <v>1760</v>
       </c>
-      <c r="Y51" s="19">
+      <c r="Y49" s="19">
         <v>1</v>
       </c>
-      <c r="Z51" s="20">
+      <c r="Z49" s="20">
         <v>8.17</v>
       </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="15">
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="15">
         <v>138</v>
       </c>
-      <c r="AD51" s="19">
+      <c r="AD49" s="19">
         <v>2031</v>
       </c>
-      <c r="AE51" s="15">
+      <c r="AE49" s="15">
         <v>0</v>
       </c>
-      <c r="AF51" s="21">
+      <c r="AF49" s="21">
         <v>4.5</v>
       </c>
-      <c r="AG51" s="22">
+      <c r="AG49" s="22">
         <v>0</v>
       </c>
-      <c r="AH51" s="20">
+      <c r="AH49" s="20">
         <v>4.09</v>
       </c>
-      <c r="AI51" s="16">
+      <c r="AI49" s="16">
         <v>0.69</v>
       </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
+      <c r="AJ49"/>
+      <c r="AK49" s="13" t="inlineStr">
         <is>
           <t>2018-12-27</t>
         </is>
       </c>
-      <c r="AL51" s="19">
+      <c r="AL49" s="19">
         <v>2832</v>
       </c>
-      <c r="AM51" s="13" t="inlineStr">
+      <c r="AM49" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AN51" s="13" t="inlineStr">
+      <c r="AN49" s="13" t="inlineStr">
         <is>
           <t>6天</t>
         </is>
       </c>
-      <c r="AO51" s="13" t="inlineStr">
+      <c r="AO49" s="13" t="inlineStr">
         <is>
           <t>2天</t>
         </is>
       </c>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="19">
+      <c r="AP49" s="4"/>
+      <c r="AQ49" s="19">
         <v>9</v>
       </c>
-      <c r="AR51" s="19">
+      <c r="AR49" s="19">
         <v>6</v>
       </c>
-      <c r="AS51" s="14" t="inlineStr">
+      <c r="AS49" s="14" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="AT51" s="13" t="inlineStr">
+      <c r="AT49" s="13" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
+      <c r="AX49" s="13"/>
+      <c r="AY49" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
+      <c r="AZ49" s="13"/>
+      <c r="BA49" s="13"/>
+      <c r="BB49" s="13"/>
+      <c r="BC49" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14" t="inlineStr">
+      <c r="BD49" s="13"/>
+      <c r="BE49" s="13"/>
+      <c r="BF49" s="13"/>
+      <c r="BG49" s="13"/>
+      <c r="BH49" s="14" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BI51" s="23" t="inlineStr">
+      <c r="BI49" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ51" s="23" t="inlineStr">
+      <c r="BJ49" s="23" t="inlineStr">
         <is>
           <t>5.9 ounces</t>
         </is>
       </c>
-      <c r="BK51" s="23" t="inlineStr">
+      <c r="BK49" s="23" t="inlineStr">
         <is>
           <t>167.26 g</t>
         </is>
       </c>
-      <c r="BL51" s="23" t="inlineStr">
+      <c r="BL49" s="23" t="inlineStr">
         <is>
           <t>5.46"L x 2.84"W x 4.46"H</t>
         </is>
       </c>
-      <c r="BM51" s="23" t="inlineStr">
+      <c r="BM49" s="23" t="inlineStr">
         <is>
           <t>13.87 x 7.21 x 11.33 cm</t>
         </is>
       </c>
-      <c r="BN51" s="23" t="inlineStr">
+      <c r="BN49" s="23" t="inlineStr">
         <is>
           <t>0.37 pounds</t>
         </is>
       </c>
-      <c r="BO51" s="23" t="inlineStr">
+      <c r="BO49" s="23" t="inlineStr">
         <is>
           <t>167.83 g</t>
         </is>
       </c>
-      <c r="BP51" s="23" t="inlineStr">
+      <c r="BP49" s="23" t="inlineStr">
         <is>
           <t>4.7 x 3.2 x 2.9 inches</t>
         </is>
       </c>
-      <c r="BQ51" s="23" t="inlineStr">
+      <c r="BQ49" s="23" t="inlineStr">
         <is>
           <t>11.94 x 8.13 x 7.37 cm</t>
         </is>
       </c>
-      <c r="BR51" s="13" t="inlineStr">
+      <c r="BR49" s="13" t="inlineStr">
         <is>
           <t>大号标准尺寸</t>
         </is>
@@ -22463,70 +21858,55 @@
     <hyperlink ref="M43" r:id="rId318" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N43" r:id="rId319"/>
     <hyperlink ref="AW43" r:id="rId320" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1C6K1RF1VZ7JZ"/>
-    <hyperlink ref="C44" r:id="rId321" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="G44" r:id="rId322" tooltip="https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId323" tooltip="https://www.amazon.com/dp/B0C7C7PLLG?psc=1"/>
-    <hyperlink ref="K44" r:id="rId324" tooltip="https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId325" tooltip="https://www.amazon.com/dp/B0GHNFPSLP"/>
-    <hyperlink ref="M44" r:id="rId326" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="C44" r:id="rId321" tooltip="https://www.amazon.com/dp/B0H2V9LVLF"/>
+    <hyperlink ref="G44" r:id="rId322" tooltip="https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0H2V9LVLF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId323" tooltip="https://www.amazon.com/dp/B0H2V9LVLF?psc=1"/>
+    <hyperlink ref="K44" r:id="rId324" tooltip="https://images-na.ssl-images-amazon.com/images/I/71DLRSID7BL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId325" tooltip="https://www.amazon.com/dp/B0HH8NB97S"/>
+    <hyperlink ref="M44" r:id="rId326" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N44" r:id="rId327"/>
-    <hyperlink ref="AW44" r:id="rId328" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3"/>
-    <hyperlink ref="C45" r:id="rId329" tooltip="https://www.amazon.com/dp/B0H2V9LVLF"/>
-    <hyperlink ref="G45" r:id="rId330" tooltip="https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0H2V9LVLF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId331" tooltip="https://www.amazon.com/dp/B0H2V9LVLF?psc=1"/>
-    <hyperlink ref="K45" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/71DLRSID7BL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId333" tooltip="https://www.amazon.com/dp/B0HH8NB97S"/>
+    <hyperlink ref="AW44" r:id="rId328" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96"/>
+    <hyperlink ref="C45" r:id="rId329" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS"/>
+    <hyperlink ref="G45" r:id="rId330" tooltip="https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0HF7K2ZKS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId331" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS?psc=1"/>
+    <hyperlink ref="K45" r:id="rId332" tooltip="https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId333" tooltip="https://www.amazon.com/dp/B0HJXGHYVB"/>
     <hyperlink ref="M45" r:id="rId334" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N45" r:id="rId335"/>
-    <hyperlink ref="AW45" r:id="rId336" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A18INPDUBKKX96"/>
-    <hyperlink ref="C46" r:id="rId337" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="G46" r:id="rId338" tooltip="https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId339" tooltip="https://www.amazon.com/dp/B0BCF8N3B4?psc=1"/>
-    <hyperlink ref="K46" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId341" tooltip="https://www.amazon.com/dp/B0DNB8M7ZM"/>
-    <hyperlink ref="M46" r:id="rId342" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="AW45" r:id="rId336" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN"/>
+    <hyperlink ref="C46" r:id="rId337" tooltip="https://www.amazon.com/dp/B0GSH62CFF"/>
+    <hyperlink ref="G46" r:id="rId338" tooltip="https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B0GSH62CFF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J46" r:id="rId339" tooltip="https://www.amazon.com/dp/B0GSH62CFF?psc=1"/>
+    <hyperlink ref="K46" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/71pXZvcdNQL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId341" tooltip="https://www.amazon.com/dp/B0H6KJWTHQ"/>
+    <hyperlink ref="M46" r:id="rId342" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N46" r:id="rId343"/>
-    <hyperlink ref="C47" r:id="rId344" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS"/>
-    <hyperlink ref="G47" r:id="rId345" tooltip="https://www.amazon.com/stores/XIEBroRobotVacuumandMop/page/63D629A5-9469-4862-85F6-A208E9F2C951?lp_asin=B0HF7K2ZKS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId346" tooltip="https://www.amazon.com/dp/B0HF7K2ZKS?psc=1"/>
-    <hyperlink ref="K47" r:id="rId347" tooltip="https://images-na.ssl-images-amazon.com/images/I/81H8Z-8RUNL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId348" tooltip="https://www.amazon.com/dp/B0HJXGHYVB"/>
-    <hyperlink ref="M47" r:id="rId349" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N47" r:id="rId350"/>
-    <hyperlink ref="AW47" r:id="rId351" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P2R2P57KGCPN"/>
-    <hyperlink ref="C48" r:id="rId352" tooltip="https://www.amazon.com/dp/B0GSH62CFF"/>
-    <hyperlink ref="G48" r:id="rId353" tooltip="https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B0GSH62CFF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId354" tooltip="https://www.amazon.com/dp/B0GSH62CFF?psc=1"/>
-    <hyperlink ref="K48" r:id="rId355" tooltip="https://images-na.ssl-images-amazon.com/images/I/71pXZvcdNQL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId356" tooltip="https://www.amazon.com/dp/B0H6KJWTHQ"/>
-    <hyperlink ref="M48" r:id="rId357" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N48" r:id="rId358"/>
-    <hyperlink ref="AW48" r:id="rId359" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P0ZBGEDS6RH6"/>
-    <hyperlink ref="C49" r:id="rId360" tooltip="https://www.amazon.com/dp/B0HFJCMP9T"/>
-    <hyperlink ref="G49" r:id="rId361" tooltip="https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJCMP9T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId362" tooltip="https://www.amazon.com/dp/B0HFJCMP9T?psc=1"/>
-    <hyperlink ref="K49" r:id="rId363" tooltip="https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId364" tooltip="https://www.amazon.com/dp/B0HK45FHVF"/>
-    <hyperlink ref="M49" r:id="rId365" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N49" r:id="rId366"/>
-    <hyperlink ref="AW49" r:id="rId367" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PGFDS4HWDNZG"/>
-    <hyperlink ref="C50" r:id="rId368" tooltip="https://www.amazon.com/dp/B07BRVNXZW"/>
-    <hyperlink ref="G50" r:id="rId369" tooltip="https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId370" tooltip="https://www.amazon.com/dp/B07BRVNXZW?psc=1"/>
-    <hyperlink ref="K50" r:id="rId371" tooltip="https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId372" tooltip="https://www.amazon.com/dp/B0GHNN4HT7"/>
-    <hyperlink ref="M50" r:id="rId373" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N50" r:id="rId374"/>
-    <hyperlink ref="AW50" r:id="rId375" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
-    <hyperlink ref="C51" r:id="rId376" tooltip="https://www.amazon.com/dp/B07KL93JBN"/>
-    <hyperlink ref="G51" r:id="rId377" tooltip="https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07KL93JBN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId378" tooltip="https://www.amazon.com/dp/B07KL93JBN?psc=1"/>
-    <hyperlink ref="K51" r:id="rId379" tooltip="https://m.media-amazon.com/images/I/31fAsdCfw7L._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId380" tooltip="https://www.amazon.com/dp/B07KL93JBN"/>
-    <hyperlink ref="M51" r:id="rId381" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N51" r:id="rId382"/>
+    <hyperlink ref="AW46" r:id="rId344" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1P0ZBGEDS6RH6"/>
+    <hyperlink ref="C47" r:id="rId345" tooltip="https://www.amazon.com/dp/B0HFJCMP9T"/>
+    <hyperlink ref="G47" r:id="rId346" tooltip="https://www.amazon.com/stores/wrydao/page/02C4FDE4-9A01-4B0F-A0AF-834F3DB667BF?lp_asin=B0HFJCMP9T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId347" tooltip="https://www.amazon.com/dp/B0HFJCMP9T?psc=1"/>
+    <hyperlink ref="K47" r:id="rId348" tooltip="https://images-na.ssl-images-amazon.com/images/I/615uGhFYDUL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId349" tooltip="https://www.amazon.com/dp/B0HK45FHVF"/>
+    <hyperlink ref="M47" r:id="rId350" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N47" r:id="rId351"/>
+    <hyperlink ref="AW47" r:id="rId352" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PGFDS4HWDNZG"/>
+    <hyperlink ref="C48" r:id="rId353" tooltip="https://www.amazon.com/dp/B07BRVNXZW"/>
+    <hyperlink ref="G48" r:id="rId354" tooltip="https://www.amazon.com/stores/Roborock/page/69ADA24D-41D1-454D-9AAC-68D2B6252352?lp_asin=B07BRVNXZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId355" tooltip="https://www.amazon.com/dp/B07BRVNXZW?psc=1"/>
+    <hyperlink ref="K48" r:id="rId356" tooltip="https://m.media-amazon.com/images/I/21Oz8FY385L._SX600_SY600_CR,0,0,600,600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId357" tooltip="https://www.amazon.com/dp/B0GHNN4HT7"/>
+    <hyperlink ref="M48" r:id="rId358" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N48" r:id="rId359"/>
+    <hyperlink ref="AW48" r:id="rId360" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2NZXCP1D8DIIH"/>
+    <hyperlink ref="C49" r:id="rId361" tooltip="https://www.amazon.com/dp/B07KL93JBN"/>
+    <hyperlink ref="G49" r:id="rId362" tooltip="https://www.amazon.com/stores/iRobot%C2%AE/page/A144A34F-3D29-45A4-9DF7-8E77C31F8C7F?lp_asin=B07KL93JBN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId363" tooltip="https://www.amazon.com/dp/B07KL93JBN?psc=1"/>
+    <hyperlink ref="K49" r:id="rId364" tooltip="https://m.media-amazon.com/images/I/31fAsdCfw7L._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId365" tooltip="https://www.amazon.com/dp/B07KL93JBN"/>
+    <hyperlink ref="M49" r:id="rId366" tooltip="https://www.amazon.com/b?node=3743561"/>
+    <hyperlink ref="N49" r:id="rId367"/>
   </hyperlinks>
-  <drawing r:id="rId383"/>
+  <drawing r:id="rId368"/>
 </worksheet>
 </file>
 
@@ -22596,7 +21976,7 @@
         <v>585.854045683314</v>
       </c>
       <c r="G2" s="22">
-        <v>0.22499346708864434</v>
+        <v>0.23565129244804867</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22617,7 +21997,7 @@
         <v>344.96781006481683</v>
       </c>
       <c r="G3" s="22">
-        <v>0.1328939345547458</v>
+        <v>0.13918905220476432</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22638,7 +22018,7 @@
         <v>270.19373685440524</v>
       </c>
       <c r="G4" s="22">
-        <v>0.16565527520493986</v>
+        <v>0.1735022807906741</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22659,7 +22039,7 @@
         <v>531.6055306074214</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08189851243188835</v>
+        <v>0.08577800304105423</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22669,18 +22049,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>6289</v>
+        <v>4187</v>
       </c>
       <c r="C6" s="15">
-        <v>2409473</v>
+        <v>2356944</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>383.1249801240261</v>
+        <v>562.9195127776451</v>
       </c>
       <c r="G6" s="22">
-        <v>0.06086737706028667</v>
+        <v>0.04244298023314749</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22701,49 +22081,49 @@
         <v>553.8751918158567</v>
       </c>
       <c r="G7" s="22">
-        <v>0.018921246963406017</v>
+        <v>0.019817536746071972</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>eufy</t>
+          <t>ROPVACNIC</t>
         </is>
       </c>
       <c r="B8" s="15">
-        <v>8302</v>
+        <v>9971</v>
       </c>
       <c r="C8" s="15">
-        <v>1051317</v>
+        <v>997000</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
       <c r="F8" s="20">
-        <v>126.63418453384726</v>
+        <v>99.9899709156554</v>
       </c>
       <c r="G8" s="22">
-        <v>0.08034997048091906</v>
+        <v>0.10107450582868728</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>ROPVACNIC</t>
+          <t>eufy</t>
         </is>
       </c>
       <c r="B9" s="15">
-        <v>9971</v>
+        <v>5731</v>
       </c>
       <c r="C9" s="15">
-        <v>997000</v>
+        <v>974213</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
       <c r="F9" s="20">
-        <v>99.9899709156554</v>
+        <v>169.99005409178153</v>
       </c>
       <c r="G9" s="22">
-        <v>0.09650319870696747</v>
+        <v>0.05809427268119615</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22764,7 +22144,7 @@
         <v>134.3295631825273</v>
       </c>
       <c r="G10" s="22">
-        <v>0.04963076952856576</v>
+        <v>0.051981753674607195</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22785,7 +22165,7 @@
         <v>98.9948261589404</v>
       </c>
       <c r="G11" s="22">
-        <v>0.046765966919272574</v>
+        <v>0.048981246832235176</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22806,7 +22186,7 @@
         <v>129.72672955974843</v>
       </c>
       <c r="G12" s="22">
-        <v>0.030777271275514648</v>
+        <v>0.032235174860618346</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22827,7 +22207,7 @@
         <v>174.71280991735537</v>
       </c>
       <c r="G13" s="22">
-        <v>0.004684339401682103</v>
+        <v>0.0049062341611758745</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22848,7 +22228,7 @@
         <v>299.98920863309354</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0026905916398091423</v>
+        <v>0.0028180435884439937</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22869,7 +22249,7 @@
         <v>149.99137931034483</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0033680787433582066</v>
+        <v>0.0035276229092752152</v>
       </c>
     </row>
   </sheetData>
@@ -22944,7 +22324,7 @@
         <v>585.854045683314</v>
       </c>
       <c r="G2" s="22">
-        <v>0.22499346708864434</v>
+        <v>0.23565129244804867</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22954,18 +22334,18 @@
         </is>
       </c>
       <c r="B3" s="15">
-        <v>32645</v>
+        <v>30543</v>
       </c>
       <c r="C3" s="15">
-        <v>12207860</v>
+        <v>12155331</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="20">
-        <v>373.95803338949304</v>
+        <v>397.9743640113938</v>
       </c>
       <c r="G3" s="22">
-        <v>0.31595094993370304</v>
+        <v>0.3096097313735428</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22986,49 +22366,49 @@
         <v>280.6298332896919</v>
       </c>
       <c r="G4" s="22">
-        <v>0.11088528207659476</v>
+        <v>0.11613786112519006</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Anker EufyHome</t>
+          <t>Smart Home T</t>
         </is>
       </c>
       <c r="B5" s="15">
-        <v>8302</v>
+        <v>9971</v>
       </c>
       <c r="C5" s="15">
-        <v>1051317</v>
+        <v>997000</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>126.63418453384726</v>
+        <v>99.9899709156554</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08034997048091906</v>
+        <v>0.10107450582868728</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Smart Home T</t>
+          <t>Anker EufyHome</t>
         </is>
       </c>
       <c r="B6" s="15">
-        <v>9971</v>
+        <v>5731</v>
       </c>
       <c r="C6" s="15">
-        <v>997000</v>
+        <v>974213</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>99.9899709156554</v>
+        <v>169.99005409178153</v>
       </c>
       <c r="G6" s="22">
-        <v>0.09650319870696747</v>
+        <v>0.05809427268119615</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23049,7 +22429,7 @@
         <v>1199.9895424836602</v>
       </c>
       <c r="G7" s="22">
-        <v>0.00740396620307192</v>
+        <v>0.0077546882919412065</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23070,7 +22450,7 @@
         <v>367.7301341589267</v>
       </c>
       <c r="G8" s="22">
-        <v>0.018756714381115532</v>
+        <v>0.019645210339584388</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23091,7 +22471,7 @@
         <v>134.3295631825273</v>
       </c>
       <c r="G9" s="22">
-        <v>0.04963076952856576</v>
+        <v>0.051981753674607195</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23112,7 +22492,7 @@
         <v>98.9948261589404</v>
       </c>
       <c r="G10" s="22">
-        <v>0.046765966919272574</v>
+        <v>0.048981246832235176</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23133,7 +22513,7 @@
         <v>398.99064171122996</v>
       </c>
       <c r="G11" s="22">
-        <v>0.007239433620781433</v>
+        <v>0.007582361885453624</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23154,7 +22534,7 @@
         <v>89.98995395562997</v>
       </c>
       <c r="G12" s="22">
-        <v>0.02312166700541022</v>
+        <v>0.024216928535225547</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23175,7 +22555,7 @@
         <v>249.7408343868521</v>
       </c>
       <c r="G13" s="22">
-        <v>0.00765560427010443</v>
+        <v>0.008018246325392803</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23196,7 +22576,7 @@
         <v>299.98920863309354</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0026905916398091423</v>
+        <v>0.0028180435884439937</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23217,7 +22597,7 @@
         <v>239.08846153846153</v>
       </c>
       <c r="G15" s="22">
-        <v>0.002516380670325097</v>
+        <v>0.0026355803345159655</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23238,7 +22618,7 @@
         <v>149.99137931034483</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0033680787433582066</v>
+        <v>0.0035276229092752152</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -23259,7 +22639,7 @@
         <v>99.99107142857143</v>
       </c>
       <c r="G17" s="22">
-        <v>0.002167958731357007</v>
+        <v>0.0022706538266599086</v>
       </c>
     </row>
   </sheetData>
